--- a/缓存数据/PotentialIndustries.xlsx
+++ b/缓存数据/PotentialIndustries.xlsx
@@ -472,25 +472,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>397494.1899999999</v>
+        <v>411840.6</v>
       </c>
       <c r="C2" t="n">
-        <v>284073.79</v>
+        <v>304697.4</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>60674.73999999999</v>
+        <v>60871.12</v>
       </c>
       <c r="F2" t="n">
-        <v>39403.03</v>
+        <v>32234.5</v>
       </c>
       <c r="G2" t="n">
-        <v>516.9499999999999</v>
+        <v>257.51</v>
       </c>
       <c r="H2" t="n">
-        <v>12825.68</v>
+        <v>13780.07</v>
       </c>
     </row>
     <row r="3">
@@ -500,25 +500,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>411840.6</v>
+        <v>441579.5200000001</v>
       </c>
       <c r="C3" t="n">
-        <v>304697.4</v>
+        <v>332925.88</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>60871.12000000001</v>
+        <v>62402.15000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>32234.5</v>
+        <v>29809.53</v>
       </c>
       <c r="G3" t="n">
-        <v>257.51</v>
+        <v>334.31</v>
       </c>
       <c r="H3" t="n">
-        <v>13780.07</v>
+        <v>16107.65</v>
       </c>
     </row>
     <row r="4">
@@ -528,25 +528,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>441579.5200000001</v>
+        <v>459916.47</v>
       </c>
       <c r="C4" t="n">
-        <v>332925.88</v>
+        <v>348927.26</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>62402.15000000002</v>
+        <v>63136.28000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>29809.53</v>
+        <v>25626.8</v>
       </c>
       <c r="G4" t="n">
-        <v>334.31</v>
+        <v>275.7</v>
       </c>
       <c r="H4" t="n">
-        <v>16107.65</v>
+        <v>21950.43</v>
       </c>
     </row>
     <row r="5">
@@ -556,25 +556,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>459916.47</v>
+        <v>416086.39</v>
       </c>
       <c r="C5" t="n">
-        <v>348927.26</v>
+        <v>310944.56</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>63136.28</v>
+        <v>64026.97</v>
       </c>
       <c r="F5" t="n">
-        <v>25626.8</v>
+        <v>21094.83999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>275.7</v>
+        <v>267.2</v>
       </c>
       <c r="H5" t="n">
-        <v>21950.43</v>
+        <v>19752.82000000001</v>
       </c>
     </row>
     <row r="6">
@@ -584,25 +584,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>416086.39</v>
+        <v>405755.7499999999</v>
       </c>
       <c r="C6" t="n">
-        <v>310944.56</v>
+        <v>289494.47</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>64026.97000000001</v>
+        <v>66490.10000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>21094.84</v>
+        <v>32703.94</v>
       </c>
       <c r="G6" t="n">
-        <v>267.2</v>
+        <v>219.11</v>
       </c>
       <c r="H6" t="n">
-        <v>19752.82000000001</v>
+        <v>16848.13</v>
       </c>
     </row>
     <row r="7">
@@ -612,25 +612,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>405755.7499999999</v>
+        <v>429172.74</v>
       </c>
       <c r="C7" t="n">
-        <v>289494.47</v>
+        <v>317400.79</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>66490.10000000001</v>
+        <v>58943.99000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>32703.94000000001</v>
+        <v>35520.68</v>
       </c>
       <c r="G7" t="n">
-        <v>219.11</v>
+        <v>233.76</v>
       </c>
       <c r="H7" t="n">
-        <v>16848.13</v>
+        <v>17073.52</v>
       </c>
     </row>
     <row r="8">
@@ -640,25 +640,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>429172.74</v>
+        <v>450327.23</v>
       </c>
       <c r="C8" t="n">
-        <v>317400.79</v>
+        <v>336229.98</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>58943.99000000001</v>
+        <v>59567.52999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>35520.68</v>
+        <v>33442.59</v>
       </c>
       <c r="G8" t="n">
-        <v>233.76</v>
+        <v>629.98</v>
       </c>
       <c r="H8" t="n">
-        <v>17073.52</v>
+        <v>20457.15</v>
       </c>
     </row>
     <row r="9">
@@ -668,25 +668,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>450327.23</v>
+        <v>479971.97</v>
       </c>
       <c r="C9" t="n">
-        <v>336229.98</v>
+        <v>366418.71</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>59567.53</v>
+        <v>59097.08</v>
       </c>
       <c r="F9" t="n">
-        <v>33442.59</v>
+        <v>33452.77999999998</v>
       </c>
       <c r="G9" t="n">
-        <v>629.98</v>
+        <v>591.88</v>
       </c>
       <c r="H9" t="n">
-        <v>20457.15</v>
+        <v>20411.52</v>
       </c>
     </row>
   </sheetData>

--- a/缓存数据/PotentialIndustries.xlsx
+++ b/缓存数据/PotentialIndustries.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -53,18 +53,18 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -472,25 +472,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>411840.6</v>
+        <v>410466.7299999999</v>
       </c>
       <c r="C2" t="n">
-        <v>304697.4</v>
+        <v>295312.34</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>60871.12</v>
+        <v>49565.64000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>32234.5</v>
+        <v>52572.70999999998</v>
       </c>
       <c r="G2" t="n">
-        <v>257.51</v>
+        <v>407.61</v>
       </c>
       <c r="H2" t="n">
-        <v>13780.07</v>
+        <v>12608.43</v>
       </c>
     </row>
     <row r="3">
@@ -500,25 +500,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>441579.5200000001</v>
+        <v>413079.39</v>
       </c>
       <c r="C3" t="n">
-        <v>332925.88</v>
+        <v>299022.53</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>62402.15000000001</v>
+        <v>49813.44999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>29809.53</v>
+        <v>53706.50999999998</v>
       </c>
       <c r="G3" t="n">
-        <v>334.31</v>
+        <v>430.5</v>
       </c>
       <c r="H3" t="n">
-        <v>16107.65</v>
+        <v>10106.4</v>
       </c>
     </row>
     <row r="4">
@@ -528,25 +528,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>459916.47</v>
+        <v>382226.4799999999</v>
       </c>
       <c r="C4" t="n">
-        <v>348927.26</v>
+        <v>272513.83</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>63136.28000000001</v>
+        <v>51952.47</v>
       </c>
       <c r="F4" t="n">
-        <v>25626.8</v>
+        <v>45990.34000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>275.7</v>
+        <v>403.22</v>
       </c>
       <c r="H4" t="n">
-        <v>21950.43</v>
+        <v>11366.62</v>
       </c>
     </row>
     <row r="5">
@@ -556,25 +556,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>416086.39</v>
+        <v>350155.4</v>
       </c>
       <c r="C5" t="n">
-        <v>310944.56</v>
+        <v>243675.95</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>64026.97</v>
+        <v>49867.09</v>
       </c>
       <c r="F5" t="n">
-        <v>21094.83999999999</v>
+        <v>42178.11</v>
       </c>
       <c r="G5" t="n">
-        <v>267.2</v>
+        <v>431.45</v>
       </c>
       <c r="H5" t="n">
-        <v>19752.82000000001</v>
+        <v>14002.8</v>
       </c>
     </row>
     <row r="6">
@@ -584,25 +584,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>405755.7499999999</v>
+        <v>394342.0699999999</v>
       </c>
       <c r="C6" t="n">
-        <v>289494.47</v>
+        <v>293384.41</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>66490.10000000001</v>
+        <v>54506.28999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>32703.94</v>
+        <v>32429.3</v>
       </c>
       <c r="G6" t="n">
-        <v>219.11</v>
+        <v>516.04</v>
       </c>
       <c r="H6" t="n">
-        <v>16848.13</v>
+        <v>13506.03</v>
       </c>
     </row>
     <row r="7">
@@ -612,25 +612,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>429172.74</v>
+        <v>457970.8099999999</v>
       </c>
       <c r="C7" t="n">
-        <v>317400.79</v>
+        <v>352512.5</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>58943.99000000001</v>
+        <v>56731.48999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>35520.68</v>
+        <v>34487.40999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>233.76</v>
+        <v>428.99</v>
       </c>
       <c r="H7" t="n">
-        <v>17073.52</v>
+        <v>13810.42</v>
       </c>
     </row>
     <row r="8">
@@ -640,25 +640,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>450327.23</v>
+        <v>397868.48</v>
       </c>
       <c r="C8" t="n">
-        <v>336229.98</v>
+        <v>294135.18</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>59567.52999999999</v>
+        <v>50201.35</v>
       </c>
       <c r="F8" t="n">
-        <v>33442.59</v>
+        <v>41896.03000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>629.98</v>
+        <v>397.93</v>
       </c>
       <c r="H8" t="n">
-        <v>20457.15</v>
+        <v>11237.99</v>
       </c>
     </row>
     <row r="9">
@@ -668,28 +668,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>479971.97</v>
+        <v>374615.74</v>
       </c>
       <c r="C9" t="n">
-        <v>366418.71</v>
+        <v>273853.14</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>59097.08</v>
+        <v>45190.69</v>
       </c>
       <c r="F9" t="n">
-        <v>33452.77999999998</v>
+        <v>43127.15000000002</v>
       </c>
       <c r="G9" t="n">
-        <v>591.88</v>
+        <v>396.41</v>
       </c>
       <c r="H9" t="n">
-        <v>20411.52</v>
+        <v>12048.35</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>